--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.7683811499779</v>
+        <v>2.074861936871409</v>
       </c>
       <c r="D2" t="n">
-        <v>12.56280570478043</v>
+        <v>2.041455927026819</v>
       </c>
       <c r="E2" t="n">
-        <v>4.599344153849765</v>
+        <v>0.7473934250005868</v>
       </c>
       <c r="F2" t="n">
-        <v>4.449602119295054</v>
+        <v>0.7230603443854463</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1.591038948461973</v>
+        <v>0.2585438291250707</v>
       </c>
       <c r="D3" t="n">
-        <v>1.751928224918474</v>
+        <v>0.2846883365492521</v>
       </c>
       <c r="E3" t="n">
-        <v>4.599344153849765</v>
+        <v>0.7473934250005868</v>
       </c>
       <c r="F3" t="n">
-        <v>4.449602119295054</v>
+        <v>0.7230603443854463</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.957778836899717</v>
+        <v>0.9681390609962041</v>
       </c>
       <c r="D4" t="n">
-        <v>5.957778836899717</v>
+        <v>0.9681390609962041</v>
       </c>
       <c r="E4" t="n">
-        <v>4.599344153849765</v>
+        <v>0.7473934250005868</v>
       </c>
       <c r="F4" t="n">
-        <v>4.449602119295054</v>
+        <v>0.7230603443854463</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
